--- a/licitaciones.xlsx
+++ b/licitaciones.xlsx
@@ -18,10 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -105,14 +104,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -127,9 +126,6 @@
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -137,9 +133,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -817,7 +810,7 @@
           <t>APF</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Infraestructura, Comunicaciones y Transportes</t>
         </is>
@@ -834,7 +827,7 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>Centro Sict Quintana Roo, Subdireccion de Obras</t>
+          <t>Centro Sict Quintana Roo, Subdirección de Obras</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
@@ -847,14 +840,14 @@
           <t>Trabajos de Mantenimiento de los Inmuebles Centro Sict Quintana Roo Chetumal y Campamento de Huay Pix en el Estado de Quintana Roo</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>Descripcion del Contrato</t>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Descripción del Contrato</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>Adjudicacion Directa Por Montos Maximos Por Excepcion</t>
+          <t>Adjudicación Directa Por Montos Máximos Por Excepción</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -864,12 +857,12 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>Art. 43</t>
-        </is>
-      </c>
-      <c r="Q3" s="7" t="inlineStr">
-        <is>
-          <t>Obras Publicas o Servicios Relacionados con las Mismas, Dentro de los Montos Maximos Establecidos en el Pef.</t>
+          <t>ART. 43</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>Obras Públicas o Servicios Relacionados con las Mismas, Dentro de los Montos Máximos Establecidos en el Pef.</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -893,12 +886,14 @@
       <c r="V3" s="8" t="n">
         <v>46203</v>
       </c>
-      <c r="W3" s="9" t="n">
-        <v>383004.84</v>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>383004.84</t>
+        </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>Grupo Cis Hg Sa de Cv</t>
+          <t>GRUPO CIS HG SA DE CV</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
@@ -928,153 +923,155 @@
         </is>
       </c>
       <c r="AE3" s="6" t="n"/>
-      <c r="AF3" s="8" t="n"/>
-      <c r="AG3" s="8" t="n"/>
+      <c r="AF3" s="6" t="n"/>
+      <c r="AG3" s="6" t="n"/>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>C-2026-00060983</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>E-2026-00034589</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>AO-16-B00-016B00004-N-61-2026</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>C-2026-00060983</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>APF</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Medio Ambiente y Recursos Naturales</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>APF</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>Comision Nacional del Agua</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Organismo de Cuenca Aguas del Valle de Mexico, Direccion de Administracion</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>Construccion del Centro de Visualizacion (Rehabilitacion y Modernizacion del Cen</t>
-        </is>
-      </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>Construccion del Centro de Visualizacion (Rehabilitacion y Modernizacion del Centro de Visualizacion en la Ptar Atotonilco).</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr">
-        <is>
-          <t>Descripcion del Contrato</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>Adjudicacion Directa Por Licitaciones Publicas Desiertas</t>
-        </is>
-      </c>
-      <c r="O4" s="10" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Construcción del Centro de Visualización (Rehabilitación y Modernización del Cen</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Construcción del Centro de Visualización (Rehabilitación y Modernización del Centro de Visualización en la Ptar Atotonilco).</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>Descripción del Contrato</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>Adjudicación Directa Por Licitaciones Públicas Desiertas</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="P4" s="10" t="inlineStr">
-        <is>
-          <t>Art. 42 Fr. Vii</t>
-        </is>
-      </c>
-      <c r="Q4" s="11" t="inlineStr">
-        <is>
-          <t>Se Haya Declarado Desierta Una Licitacion Publica, Siempre Que Se Mantengan los Requisitos Establecidos en la Convocatoria.</t>
-        </is>
-      </c>
-      <c r="R4" s="10" t="inlineStr">
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>ART. 42 FR. VII</t>
+        </is>
+      </c>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>Se Haya Declarado Desierta Una Licitación Pública, Siempre Que Se Mantengan los Requisitos Establecidos en la Convocatoria.</t>
+        </is>
+      </c>
+      <c r="R4" s="9" t="inlineStr">
         <is>
           <t>62602</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="9" t="inlineStr">
         <is>
           <t>Adjudicado</t>
         </is>
       </c>
-      <c r="T4" s="10" t="inlineStr">
+      <c r="T4" s="9" t="inlineStr">
         <is>
           <t>(Sin Convocatoria Vinculada en Esta Descarga)</t>
         </is>
       </c>
-      <c r="U4" s="12" t="n">
+      <c r="U4" s="11" t="n">
         <v>46203.76793981482</v>
       </c>
-      <c r="V4" s="12" t="n">
+      <c r="V4" s="11" t="n">
         <v>46158</v>
       </c>
-      <c r="W4" s="13" t="n">
-        <v>16981753.16</v>
-      </c>
-      <c r="X4" s="10" t="inlineStr">
-        <is>
-          <t>Spheral Business Group Sa de Cv</t>
-        </is>
-      </c>
-      <c r="Y4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
+        <is>
+          <t>16981753.16</t>
+        </is>
+      </c>
+      <c r="X4" s="9" t="inlineStr">
+        <is>
+          <t>SPHERAL BUSINESS GROUP SA DE CV</t>
+        </is>
+      </c>
+      <c r="Y4" s="9" t="inlineStr">
         <is>
           <t>SBG151117455</t>
         </is>
       </c>
-      <c r="Z4" s="10" t="inlineStr">
+      <c r="Z4" s="9" t="inlineStr">
         <is>
           <t>Micro</t>
         </is>
       </c>
-      <c r="AA4" s="12" t="n">
+      <c r="AA4" s="11" t="n">
         <v>46158</v>
       </c>
-      <c r="AB4" s="12" t="n">
+      <c r="AB4" s="11" t="n">
         <v>46386</v>
       </c>
-      <c r="AC4" s="10" t="inlineStr">
+      <c r="AC4" s="9" t="inlineStr">
         <is>
           <t>FALLO (contrato adjudicado)</t>
         </is>
       </c>
-      <c r="AD4" s="10" t="inlineStr">
+      <c r="AD4" s="9" t="inlineStr">
         <is>
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/295863e8280c42afb0fe6b3e91e1af78/procedimiento</t>
         </is>
       </c>
-      <c r="AE4" s="10" t="n"/>
-      <c r="AF4" s="12" t="n"/>
-      <c r="AG4" s="12" t="n"/>
+      <c r="AE4" s="9" t="n"/>
+      <c r="AF4" s="9" t="n"/>
+      <c r="AG4" s="9" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -1103,7 +1100,7 @@
           <t>APF</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Marina</t>
         </is>
@@ -1125,22 +1122,22 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Construccion de Barda Colindante Paralela Al Brazo Izquierdo</t>
+          <t>Construcción de Barda Colindante Paralela Al Brazo Izquierdo</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Construccion de Barda Colindante Paralela Al Brazo Izquierdo en Zona Norte de la Isla de la Palma en el Puerto de Lazaro Cardenas, Mich.</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>Descripcion Anuncio</t>
+          <t>Construcción de Barda Colindante Paralela Al Brazo Izquierdo en Zona Norte de la Isla de la Palma en el Puerto de Lázaro Cárdenas, Mich.</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Descripción Anuncio</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Publica</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -1149,7 +1146,7 @@
         </is>
       </c>
       <c r="P5" s="6" t="n"/>
-      <c r="Q5" s="7" t="n"/>
+      <c r="Q5" s="6" t="n"/>
       <c r="R5" s="6" t="inlineStr">
         <is>
           <t>62601</t>
@@ -1175,11 +1172,11 @@
       <c r="X5" s="6" t="n"/>
       <c r="Y5" s="6" t="n"/>
       <c r="Z5" s="6" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="8" t="n"/>
+      <c r="AA5" s="6" t="n"/>
+      <c r="AB5" s="6" t="n"/>
       <c r="AC5" s="6" t="inlineStr">
         <is>
-          <t>CONVOCATORIA (sin fallo aun)</t>
+          <t>CONVOCATORIA (sin fallo aún)</t>
         </is>
       </c>
       <c r="AD5" s="6" t="inlineStr">
@@ -1189,7 +1186,7 @@
       </c>
       <c r="AE5" s="6" t="inlineStr">
         <is>
-          <t>Michoacan de Ocampo</t>
+          <t>Michoacán de Ocampo</t>
         </is>
       </c>
       <c r="AF5" s="8" t="n">
